--- a/analysis/tables/pythia-31m.xlsx
+++ b/analysis/tables/pythia-31m.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3977270791895768</v>
+        <v>0.289015010877759</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.09108752459720967</v>
+        <v>-0.04866330281698814</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.398x - 0.091</t>
+          <t>y = 0.289x - 0.049</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.381057181492149</v>
+        <v>0.3810571814921489</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07202363464535218</v>
+        <v>0.07202363464535219</v>
       </c>
       <c r="I3" t="n">
-        <v>0.229020173287705</v>
+        <v>0.1683763852583097</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3066395545923671</v>
+        <v>0.2403517080607709</v>
       </c>
       <c r="K3" t="n">
         <v>0.05258799584963241</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>371.1051983931052</v>
+        <v>0.2885422960167966</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07179079088517311</v>
+        <v>-0.0455421623664336</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 371.105x + 0.072</t>
+          <t>y = 0.289x - 0.046</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.549336610635078</v>
+        <v>0.3844171117543342</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06905231712819572</v>
+        <v>0.07196430820423395</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0001934513210702222</v>
+        <v>0.1578353087055996</v>
       </c>
       <c r="J4" t="n">
-        <v>371.1769891839904</v>
+        <v>0.243000133650363</v>
       </c>
       <c r="K4" t="n">
         <v>0.05258799584963241</v>
